--- a/AAII_Financials/Quarterly/TJX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TJX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>TJX</t>
   </si>
@@ -656,503 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43953</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43862</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43771</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43680</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43589</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43498</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43407</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43316</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43134</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43036</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42945</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42854</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42763</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15180000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14323000</v>
+      </c>
+      <c r="F8" s="3">
         <v>17743000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>15117000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>14401000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>13111000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>16350000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>14063000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>13468000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>12479000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>16411000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>13265000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>12758000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>11783000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>14520200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>12166300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>11843000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>11406500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>13854400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>12531900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>12077100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>10086700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>10943200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>10117300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6667600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4408900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>12206500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>10451300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>9781600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>9277600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>11127300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>9825800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>9331100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>8688700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>10960700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>8762200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>8357700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>7784000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>9467600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>8291700</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10439000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9843000</v>
+      </c>
+      <c r="F9" s="3">
         <v>12267000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>10190000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>9976000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>9246000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>11371000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>9622000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>9380000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>8739000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>11528000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>9139000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>8910000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>8374000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>10731700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>8622600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>8571600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>8223200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>10094500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>8835500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>8528100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>7255600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>7882600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>7062300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>5174500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>4439900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>7949900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>6664900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>6309800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>5940200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>7901100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>6995200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>6657400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>6214500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>7870100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>6131400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>6019800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>5521900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>6789800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>5822400</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4741000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4480000</v>
+      </c>
+      <c r="F10" s="3">
         <v>5476000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4927000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>4425000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3865000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>4979000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>4441000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4088000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3740000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>4883000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>4126000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3848000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>3409000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3788500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3543700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>3271500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3183300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>3759900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>3696400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3549000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2831100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3060600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>3055000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1493100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>4256600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3786400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3471800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>3337400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>3226200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>2830600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>2673700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>2474200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>3090600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>2630800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>2337900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>2262100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>2677800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>2469300</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1218,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1313,8 +1339,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,13 +1464,19 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-331000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1473,131 +1511,137 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>217600</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>242200</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>312200</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>36100</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3">
         <v>99300</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3">
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>336000</v>
+      </c>
+      <c r="F15" s="3">
         <v>327000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>316000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>308000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>296000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>309000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>266000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>265000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>264000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>252000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>245000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>235000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>232000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1670,8 +1714,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1760,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13524000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12637000</v>
+      </c>
+      <c r="F17" s="3">
         <v>15389000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>13229000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>12781000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>11795000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>14503000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>12370000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>12046000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11139000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>14622000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11717000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>11469000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>10612000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>13204700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>10807500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>10746400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>10535400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>12590400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>11132200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>10994100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>9320600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>10387900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>9051600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6702000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>5748200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>10856800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>9320500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>8751900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>8361300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>9786300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>8788500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>8373500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>7763500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>9859900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>7717100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>7509100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>6930200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>8360800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>7378500</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1656000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1686000</v>
+      </c>
+      <c r="F18" s="3">
         <v>2354000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1888000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1620000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1316000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1847000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1693000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1422000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1340000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1789000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1548000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1289000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1171000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1315500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1358800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1096600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>871100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1264000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1399700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1083000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>766100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>555300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1065700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-34400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1339300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1349700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1130800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1029700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>916300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1341000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1037300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>957600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>925200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>1100800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>1045100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>848600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>853800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>1106800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>913200</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,8 +2055,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2032,205 +2098,217 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>43400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>21400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>10000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>4500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>28100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>6200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>6500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>34800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-145800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>25700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>50900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>46100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>27500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-8800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>59100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-5200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>2000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1996000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2022000</v>
+      </c>
+      <c r="F21" s="3">
         <v>2681000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2204000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1928000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1612000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2156000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1959000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1687000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1604000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2041000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1793000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1524000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1403000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1589800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1598600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1324700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1093200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1484600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1618200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1299200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>982600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>769600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1289200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>187000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1091800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1560900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1356600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1251800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1163300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>1267900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>1212500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1163600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>1321900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>1220600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1083400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>1021000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>1275200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>1074400</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2238,28 +2316,28 @@
         <v>19000</v>
       </c>
       <c r="E22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="F22" s="3">
         <v>19000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="H22" s="3">
         <v>18000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>18000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>17000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>20000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>20000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>19000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>19000</v>
       </c>
       <c r="M22" s="3">
         <v>19000</v>
@@ -2268,326 +2346,344 @@
         <v>19000</v>
       </c>
       <c r="O22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>22000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>20000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>21000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>21000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>21300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>21300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>22100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>29700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>45900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>49200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>54200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>59000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>31600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>14700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>14900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>14900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>14600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>16700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>16500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>16000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>15700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>15900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>16300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>16000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>16000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>15200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2018000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1721000</v>
+      </c>
+      <c r="F23" s="3">
         <v>2390000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1916000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1647000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1346000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1889000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1736000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1468000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1390000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1843000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1589000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1327000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1208000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1338900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1359200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1085600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>852300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1242900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1379000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1054300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>721300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>508100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1016000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-92000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1342800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1326300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1122100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>1021300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>936500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>1178600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>1046500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>992600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>955600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>1112400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>1020000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>891700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>832500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>1093700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>889800</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>389000</v>
+      </c>
+      <c r="F24" s="3">
         <v>617000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>474000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>404000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>310000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>491000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>439000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>369000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>320000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>440000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>398000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>338000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>317000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>300500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>296400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>276300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>264800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>302700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>356000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>268700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>187400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>182600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>149300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>122200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-455400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>341500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>293900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>262300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>236300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>337000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>284300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>252900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>239200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>323100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>378600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>338700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>296200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>415700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>340000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2801,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1773000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1442000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1243000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1036000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1398000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1297000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1099000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1070000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1403000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1191000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>989000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>891000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1038400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1062800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>809300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>587500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>940200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1023000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>785700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>533900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>325500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>866700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-214200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-887500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>984800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>828300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>759000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>700200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>841500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>762300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>739600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>716400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>789300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>641400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>553000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>536300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>677900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>549800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="F27" s="3">
         <v>1773000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1442000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1243000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1036000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1398000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1297000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1099000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1070000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1403000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1191000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>989000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>891000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1038400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1062800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>809300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>587500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>940200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1023000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>785700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>533900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>325500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>866700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-214200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-887500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>984800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>828300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>759000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>700200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>841500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>762300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>739600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>716400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>789300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>641400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>553000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>536300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>677900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>549800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3176,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,11 +3265,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3163,15 +3283,15 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>88000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3181,8 +3301,14 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3426,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,8 +3551,14 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3460,205 +3598,217 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-43400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-21400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-10000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-28100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>8700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-34800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>145800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-25700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-50900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-46100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-27500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>8800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-59100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>5200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="F33" s="3">
         <v>1773000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1442000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1243000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1036000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1398000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1297000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1099000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1070000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1403000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1191000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>989000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>891000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1038400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1062800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>809300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>587500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>940200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1023000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>785700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>533900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>325500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>866700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-214200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-887500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>984800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>828300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>759000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>700200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>841500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>762300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>739600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>716400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>877300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>641400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>553000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>536300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>677900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>549800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3926,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="F35" s="3">
         <v>1773000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1442000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1243000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1036000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1398000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1297000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1099000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1070000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1403000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1191000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>989000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>891000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1038400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1062800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>809300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>587500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>940200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1023000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>785700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>533900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>325500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>866700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-214200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-887500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>984800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>828300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>759000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>700200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>841500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>762300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>739600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>716400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>877300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>641400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>553000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>536300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>677900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>549800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43953</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43862</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43771</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43680</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43589</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43498</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43407</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43316</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43134</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43036</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42945</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42854</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42763</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4230,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,127 +4275,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6004000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5580000</v>
+      </c>
+      <c r="F41" s="3">
         <v>6230000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4640000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4639000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4255000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5335000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4718000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5250000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5059000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5600000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4290000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4550000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5025000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5477000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3364700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3531200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4295100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>6226800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>6791600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>7106000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>8775500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>10469600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>10582000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>6620400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4287800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3216800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2060200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2186400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2235100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3030200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>2711800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2872700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2681100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>2758500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>2364200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>2449300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>2669500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>2929800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>2375500</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4323,531 +4501,561 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
         <v>435900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>506200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>511600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>502800</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>457100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>543200</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>450800</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>733000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>706000</v>
+      </c>
+      <c r="F43" s="3">
         <v>610000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>724000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>705000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>638000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>618000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>717000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>634000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>604000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>588000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>696000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>696000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>633000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>682000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>713000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>667800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>630000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>632200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>701800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>737300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>685400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>497400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>649400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>749900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>654100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>386300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>442900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>377100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>393300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>346300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>517400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>485400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>368300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>327200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>365600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>323800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>334400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>258800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>321800</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7862000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>7675000</v>
+      </c>
+      <c r="F44" s="3">
         <v>7297000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>9353000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>7372000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>7127000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>6421000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>8371000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6470000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6218000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5965000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>8285000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6585000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6441000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5819000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>8328700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>7083300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>6989800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>5961600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>6633300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>5086600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>5114600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>4337400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>4997500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3744100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>4945700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>4872600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>6274800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>5087000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>5057200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>4579000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>5543400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>4498500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>4369900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>4187200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>4725900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>3864500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>3736100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>3645000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>4384200</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>58300</v>
+      </c>
+      <c r="F45" s="3">
         <v>9000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>32500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>14200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>14300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>53100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>23600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>19100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>15500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>11500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>56400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>9800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>15000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>478000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>582400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>552500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>565400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>438100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>449400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>459000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>440500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>435000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>425000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>403600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>408600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>415000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>596800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>618100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>381700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>513700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>544400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>583300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>567100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>706700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>422700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>427400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>351400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>373900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15329000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>14640000</v>
+      </c>
+      <c r="F46" s="3">
         <v>15202000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15314000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13278000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>12595000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12991000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14352000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12890000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>12409000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12664000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>13806000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12338000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>12595000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12456000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>12988800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>11834800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>12480200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>13258600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>14576100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>13389000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>15016000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>15739300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>16653900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>11517900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>10296200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>8890600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>9374600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>8268600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>8067200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>8469200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>9317000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>8440000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>8422300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>8485700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>8390000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>7567800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>7548500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>7750800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>7942300</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>566000</v>
       </c>
-      <c r="E47" s="3">
-        <v>528000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>504000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>192000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4860,11 +5068,11 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4881,38 +5089,38 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3">
         <v>196000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>184100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>199700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>199000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>0</v>
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH47" s="3">
         <v>0</v>
@@ -4938,246 +5146,264 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19721000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>19472000</v>
+      </c>
+      <c r="F48" s="3">
         <v>18550000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>17965000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>17753000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>17478000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>16987000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>16706000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>16481000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>16121000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>15967000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>15551000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>15572000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>15076000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>14869000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>14558300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>14376400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>14356000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>14124800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>14309100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>14290600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>14189500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>14026100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>14033500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>14164300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>14275600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>14385400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>14320100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>13986200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>13829000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>5255200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>5165900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>5100500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>5026100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>5006100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>4858300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>4744700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>4601000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>4532900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>4318800</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>97000</v>
+      </c>
+      <c r="F49" s="3">
         <v>204000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>95000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>95000</v>
       </c>
       <c r="G49" s="3">
         <v>95000</v>
       </c>
       <c r="H49" s="3">
-        <v>202000</v>
+        <v>95000</v>
       </c>
       <c r="I49" s="3">
         <v>95000</v>
       </c>
       <c r="J49" s="3">
-        <v>95000</v>
+        <v>202000</v>
       </c>
       <c r="K49" s="3">
         <v>95000</v>
       </c>
       <c r="L49" s="3">
+        <v>95000</v>
+      </c>
+      <c r="M49" s="3">
+        <v>95000</v>
+      </c>
+      <c r="N49" s="3">
         <v>203000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>94000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>95000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>95000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>97000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>94500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>96600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>96900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>96700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>98600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>98000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>99300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>99000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>96700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>97100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>94500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>95500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>96300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>95900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>96700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>97600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>97300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>98100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>98600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>100100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>196400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>197500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>195600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>195900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5521,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5646,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1822000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1805000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1098000</v>
       </c>
-      <c r="E52" s="3">
-        <v>1141000</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
+        <v>1669000</v>
+      </c>
+      <c r="H52" s="3">
         <v>1617000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1549000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>917000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>949000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>942000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>898000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>741000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>748000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>768000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>765000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>927000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>786800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>782800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>776700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>981400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1087200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1005800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>996600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>753100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>597300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>589400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>549900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>773500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>497700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>504300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>496200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>504000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>445000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>472900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>460100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>466200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>433000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>425600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>418400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>404300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>261800</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5896,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37115000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>36158000</v>
+      </c>
+      <c r="F54" s="3">
         <v>35767000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>35188000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>32885000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>31858000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>31749000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>32436000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30555000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29679000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>29747000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>30351000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>28922000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>28681000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>28349000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>28428500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>27090600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>27709900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>28461500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>30071000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>28783400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>30301400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>30813600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>31565500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>26568400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>25415200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>24145000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>24288700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>22855000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>22489100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>14326000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>15025200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>14111400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>14007100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>14058000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>13877700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>12935600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>12763500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>12883800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>12866800</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +6070,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,183 +6115,191 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5024000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4854000</v>
+      </c>
+      <c r="F57" s="3">
         <v>4575000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5937000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4698000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4414000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4257000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5617000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4503000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4072000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3862000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5425000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4438000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4304000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3794000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4993300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4085500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>4370600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4465400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5443000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>4413300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4433300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>4823400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>6142500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2422100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1071200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2672600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3447400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2607700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>2578400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>2644100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>3340600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>2683300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>2509100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>2488400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>2986400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>2346500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>2174700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>2230900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>2686800</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2714000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2713000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2725000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2708000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1669000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1660000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1636000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1642000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1621000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1615000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1620000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1682000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1618000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2109000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>500000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>499800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>499600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -6042,20 +6308,20 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>749700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>749400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>749200</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
@@ -6068,11 +6334,11 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
@@ -6095,484 +6361,514 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>295100</v>
+      </c>
+      <c r="F59" s="3">
         <v>4104000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>110600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>204100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>340500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3523000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>69000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>67600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>312500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3279000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>61200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>66000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>219900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6011000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>5740600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5562000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>5648000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>6002700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>5885700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5628700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5473700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>5230600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>4925200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>4475900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>3598400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>4477700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>4239700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>3993100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>4002600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>2887200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>2673200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>2454500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>2467800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>2637200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>2481600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>2310000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>2430700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>2526800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>2207700</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13360000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12855000</v>
+      </c>
+      <c r="F60" s="3">
         <v>13361000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>14001000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>11308000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10827000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11008000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>12017000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>10621000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>10100000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10451000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>11640000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>10317000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10534000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>10305000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>11233600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>10147100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>10018500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>10468100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>11328700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>10042100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>9907000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>10803700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>11817200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>7647300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>4669500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>7150200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>7687100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>6600700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>6581000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>5531400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>6013800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>5137800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>4976900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>5125500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>5468000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>4656500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>4605400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>4757700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>4894500</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11603000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>11467000</v>
+      </c>
+      <c r="F61" s="3">
         <v>10764000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>10486000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11452000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11402000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>11142000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>11072000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11030000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11027000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>10922000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>10837000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>10950000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>10727000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2859000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2858000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2857100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3355800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3354800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3353900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3352900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>5334900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>5332900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>5447200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>5445300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>7192400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2236600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2235900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2235100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2234400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2233600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2232900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>2232100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>2231400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>2230600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>2229900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>2229100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>2228400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>2227600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>2226900</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1168000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1071000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1103000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1042000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>972000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>950000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1002000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>960000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>894000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>829000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>908000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>915000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>865000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>8821000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>8672100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>8689700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>8740100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>8635500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>8943600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>8982100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>8920400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>8844300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>8734300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>8815300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>8814100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>8809900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>8823200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>8716500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>8541800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1512400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1521700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1514400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1536500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1553600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>1534300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>1509200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>1376200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>1388000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>1415600</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6986,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +7111,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7236,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26464000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>25755000</v>
+      </c>
+      <c r="F66" s="3">
         <v>25577000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>25829000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>24019000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>23355000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>23356000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>24263000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>22773000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>22177000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>22445000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>23518000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>22314000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>22259000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>21985000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>22763800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>21694000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>22114500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>22458500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>23626200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>22377100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>24162200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>24980900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>25998700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>21907800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>20676000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>18196800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>18746200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>17552400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>17357200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>9277400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>9768400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>8884400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>8744700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>8909700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>9232100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>8394800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>8210000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>8373200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>8537000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7410,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7531,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7656,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7781,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7906,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9966000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>9669000</v>
+      </c>
+      <c r="F72" s="3">
         <v>9434000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>8720000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>8198000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7851000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>7883000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7596000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7186000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6921000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>6700000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6345000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>6014000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>5864000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>5815000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>5338000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>5002900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>5163700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>5509000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>5831700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>5663500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>5192500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>4973500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>4982600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>4115900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>4330600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5422300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>4976800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>4806500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>4552500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>4461700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>4615600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>5204700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>5192700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>4962200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>4616200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>4465300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>4605700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>4558500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>4479500</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +8156,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8281,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8406,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10651000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10403000</v>
+      </c>
+      <c r="F76" s="3">
         <v>10190000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9359000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8866000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8503000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8393000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8173000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7782000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7502000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7302000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6833000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6608000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6422000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6364000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5664700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5396600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5595400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>6003000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>6444800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>6406400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>6139200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>5832700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>5566800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4660600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4739200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5948200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5542500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5302600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5131900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>5048600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>5256900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>5227100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>5262400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>5148300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>4645600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>4540800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>4553500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>4510600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>4329800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8656,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43953</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43862</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43771</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43680</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43589</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43498</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43407</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43316</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43134</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43036</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42945</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42854</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42763</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="F81" s="3">
         <v>1773000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1442000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1243000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1036000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1398000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1297000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1099000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1070000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1403000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1191000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>989000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>891000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1038400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1062800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>809300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>587500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>940200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1023000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>785700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>533900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>325500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>866700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-214200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-887500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>984800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>828300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>759000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>700200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>841500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>762300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>739600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>716400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>877300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>641400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>553000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>536300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>677900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>549800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8960,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>296000</v>
+      </c>
+      <c r="F83" s="3">
         <v>309000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>266000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>265000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>264000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>252000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>245000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>235000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>232000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>231000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>218000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>218000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>220000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>230900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>218300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>218100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>219600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>220400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>217000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>215200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>215400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>212300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>219000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>220100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>219500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>219900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>219600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>215600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>212200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>218400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>204900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>204000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>192300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>193500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>184300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>175600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>172500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>166400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>167600</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9206,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9331,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9456,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9581,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9706,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2226000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1119000</v>
+      </c>
+      <c r="F89" s="3">
         <v>3157000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1532000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1791000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>394000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2704000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1046000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1629000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>737000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2800000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1171000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1341000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>745000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>3024700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1053000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>640700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-634500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1110600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1000100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1379600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-432700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>285100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>4080000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>3357300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-3160500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>2193000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>974300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>750000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>149200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1610700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>917100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>835800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>724900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>1096200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>826400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>654600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>448400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>1514600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>928700</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9880,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-497000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-662000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-468000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-531000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-461000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-497000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-514000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-422000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-563000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-419000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-442000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-460000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-459000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-361000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-357300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-406300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-379100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-314400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-329300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-270600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-219700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-225300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-134400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-123700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-99400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-210500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-230400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-414700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-261100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-316900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-252200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-299100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-309000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-264900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-230100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-320700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-248300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-258500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-515100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-519800</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +10126,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10251,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-495000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-673000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-471000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-541000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-466000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-503000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-870000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-617000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-563000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-427000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-436000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-462000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-457000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-362000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-359800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-406900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-378900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-324500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-330800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-272900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-217900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-224900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-134400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-125400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-97700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-221100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-464200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-417500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-253500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-326700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-254300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-298200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>149400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-220500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-213400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-346600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-251100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-201800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-343600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-303700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,127 +10425,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>474000</v>
+      </c>
+      <c r="F96" s="3">
         <v>471000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>473000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>474000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>424000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>422000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>423000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>423000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>380000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>379000</v>
       </c>
       <c r="M96" s="3">
         <v>380000</v>
       </c>
       <c r="N96" s="3">
+        <v>379000</v>
+      </c>
+      <c r="O96" s="3">
+        <v>380000</v>
+      </c>
+      <c r="P96" s="3">
         <v>382000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>343000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-341300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-342500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-345700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-309500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-310300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-312700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-313600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-315200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-278300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-276500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-277600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-278700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-238800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-240300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-241400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-243600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-197300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-197100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-197500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-200900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-168600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-169100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>-170400</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10671,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10796,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,361 +10921,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1281000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1081000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1141000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-975000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-954000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1048000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1163000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-953000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-882000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-840000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1097000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-904000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1377000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-837000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-590500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-770600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1013800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-931100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1311200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1025100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-2810300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1053100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-312400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>28200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-978000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>4490500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-581400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-695500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-538400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-599600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-769900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-759600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-526000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-561500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-524100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-727600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-484100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-630200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>77000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-54000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-8000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>7000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-11000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>43000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-65000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>18000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>38000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-42000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-11000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-43000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>37600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-42100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-11900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-41700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-33400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-16500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-20900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>16600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>49300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-21200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>51000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-37800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>9200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>12500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-18100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>4000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-34000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-55800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>72900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-40700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>103900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-22900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>13500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>-49200</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>424000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-650000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1590000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>384000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1080000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>617000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-532000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>191000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-541000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1310000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-260000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-475000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-452000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>2112100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-166500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-763900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1931700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-564800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-314400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1669500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1694100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-112400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3961600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>2332600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1071100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1156600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-126200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-48700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-795200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>318500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-161000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>191600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-77400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>394200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-85100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-220200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-260400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>554300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>571900</v>
       </c>
     </row>
